--- a/artifacts/reports/architecture/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書/ARCH-HOST-01_5.1_全体構成図.xlsx
+++ b/artifacts/reports/architecture/ARCH-HOST-01_タブレットPOS_デバイスコネクタ基本設計書/ARCH-HOST-01_5.1_全体構成図.xlsx
@@ -396,182 +396,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="config_file.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9353550" y="5505450"/>
-          <a:ext cx="400050" cy="400050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="cash_changer.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16373475" y="7334250"/>
-          <a:ext cx="400050" cy="400050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3" descr="cash_drawer.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16373475" y="8934450"/>
-          <a:ext cx="400050" cy="400050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4" descr="display.png">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16373475" y="10534650"/>
-          <a:ext cx="400050" cy="400050"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
